--- a/corr_matrix/residual_exam2A_3PL.xlsx
+++ b/corr_matrix/residual_exam2A_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2A01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1467283246084426</v>
+        <v>-0.146716156383892</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.229450130631371</v>
+        <v>-0.2294066554436329</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05705987742345903</v>
+        <v>-0.05706259212450667</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1964741759017689</v>
+        <v>-0.1964586851837019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03756387538767001</v>
+        <v>0.03757729443795635</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1784560919181689</v>
+        <v>-0.1784415765892236</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1159151229227568</v>
+        <v>-0.1158901076840817</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03982221093887654</v>
+        <v>0.03979869880352869</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.08191325254965322</v>
+        <v>-0.08192416750336802</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.06768521643960035</v>
+        <v>-0.06767357511572947</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01919493272810242</v>
+        <v>0.01921096076280788</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.009079565232523209</v>
+        <v>-0.009060707402556005</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1850370713545271</v>
+        <v>-0.1850380856965045</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01211476857481954</v>
+        <v>-0.01210583301429007</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2318477249768466</v>
+        <v>-0.2318910839135059</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1467283246084426</v>
+        <v>-0.146716156383892</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3303996510074061</v>
+        <v>0.3303719413213594</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06584749377904847</v>
+        <v>0.06582547990869864</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04888220672927298</v>
+        <v>-0.04889100235188</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04537184405763093</v>
+        <v>0.04539659495292903</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2734001177142409</v>
+        <v>-0.273381486188743</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01932857342352848</v>
+        <v>0.01930778965566586</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1229926994810185</v>
+        <v>-0.1230005545376402</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09364851176332502</v>
+        <v>-0.09366840335879653</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.06971627868793651</v>
+        <v>-0.06975081974803478</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1607723438690446</v>
+        <v>-0.1607676022211366</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.05529987669693862</v>
+        <v>-0.05535635682487677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001859152292805254</v>
+        <v>0.0001575688712157499</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.03787463396277559</v>
+        <v>-0.03786636611734018</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.03085668974852612</v>
+        <v>-0.03086107200159248</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.229450130631371</v>
+        <v>-0.2294066554436329</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3303996510074061</v>
+        <v>0.3303719413213594</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01082611892808499</v>
+        <v>0.01082424007188817</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1336052249959598</v>
+        <v>-0.1336350188576601</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1485049850793327</v>
+        <v>-0.1484371975438506</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03803373771196568</v>
+        <v>0.03803800807928562</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2340925569434219</v>
+        <v>0.2340948740034836</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.02109570603491869</v>
+        <v>-0.02111232513816038</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1109258512467372</v>
+        <v>0.1109122680466117</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02217795087098894</v>
+        <v>-0.02224546256905153</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01107998381285726</v>
+        <v>0.01107258347005919</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1706482024768659</v>
+        <v>-0.1707802198543243</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1581607847017404</v>
+        <v>-0.158230431397335</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2380476139683421</v>
+        <v>-0.2380113065651576</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1241041926183611</v>
+        <v>-0.1241424911481934</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.05705987742345903</v>
+        <v>-0.05706259212450667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06584749377904847</v>
+        <v>0.06582547990869864</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01082611892808499</v>
+        <v>0.01082424007188817</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1038459061107786</v>
+        <v>0.1038363397151308</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005848520446957582</v>
+        <v>0.005865309055883354</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1944165283615287</v>
+        <v>-0.1944245335068649</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05573518744640846</v>
+        <v>-0.05572379719676506</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1694811327131412</v>
+        <v>-0.1695097466310259</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04277182292514164</v>
+        <v>-0.04278871258701188</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.03566434765378478</v>
+        <v>-0.03568942120521505</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1397350494004991</v>
+        <v>-0.1397131785997564</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01211746941085413</v>
+        <v>0.01209289242684258</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06957417140905643</v>
+        <v>0.06956125056231488</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1309002494549707</v>
+        <v>0.130899514453913</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.278697039808761</v>
+        <v>-0.2787404821215865</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1964741759017689</v>
+        <v>-0.1964586851837019</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.04888220672927298</v>
+        <v>-0.04889100235188</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1336052249959598</v>
+        <v>-0.1336350188576601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1038459061107786</v>
+        <v>0.1038363397151308</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1332823247206294</v>
+        <v>-0.1332372074830908</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08080507465314019</v>
+        <v>-0.08077964109778803</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3051989955065093</v>
+        <v>-0.3051969543323195</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2321315893074772</v>
+        <v>-0.2321303204935241</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1655304823325387</v>
+        <v>-0.165532756468342</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2209893209640608</v>
+        <v>0.2209778772288461</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09863082897096562</v>
+        <v>-0.09861107588431545</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02044944977386697</v>
+        <v>0.02042202968406572</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04714341253182439</v>
+        <v>0.04713154118594869</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2065042327310006</v>
+        <v>0.2065254987050177</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.08803049607792637</v>
+        <v>-0.08802255843130408</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03756387538767001</v>
+        <v>0.03757729443795635</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04537184405763093</v>
+        <v>0.04539659495292903</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1485049850793327</v>
+        <v>-0.1484371975438506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005848520446957582</v>
+        <v>0.005865309055883354</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1332823247206294</v>
+        <v>-0.1332372074830908</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1178772060330451</v>
+        <v>-0.1178396390931402</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1097312341929645</v>
+        <v>-0.1096837333923303</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02313709191950039</v>
+        <v>-0.02313206125994956</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1139587847293489</v>
+        <v>-0.1139394003759898</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.08547020016791816</v>
+        <v>-0.08544757584878435</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06756494252738353</v>
+        <v>-0.06751475648162174</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1521685471683165</v>
+        <v>-0.1521419069686895</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3494179731108781</v>
+        <v>-0.3493936335799296</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.01584838218885036</v>
+        <v>-0.01580446138126519</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1450644622661627</v>
+        <v>-0.1450563541036886</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1784560919181689</v>
+        <v>-0.1784415765892236</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2734001177142409</v>
+        <v>-0.273381486188743</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03803373771196568</v>
+        <v>0.03803800807928562</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1944165283615287</v>
+        <v>-0.1944245335068649</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08080507465314019</v>
+        <v>-0.08077964109778803</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1178772060330451</v>
+        <v>-0.1178396390931402</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1734814964126597</v>
+        <v>0.173469812965979</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1952861849636394</v>
+        <v>-0.1952972150142807</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04410558767273976</v>
+        <v>0.04410149889114259</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002172860838622796</v>
+        <v>-0.002162432814843489</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09602905280759723</v>
+        <v>0.09603059014993211</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02632978628227742</v>
+        <v>-0.02634511499826643</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.01338062164499971</v>
+        <v>-0.01339056438744992</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3928312768685449</v>
+        <v>-0.3927946649926491</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.06485449697988024</v>
+        <v>-0.06487133062601888</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1159151229227568</v>
+        <v>-0.1158901076840817</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01932857342352848</v>
+        <v>0.01930778965566586</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2340925569434219</v>
+        <v>0.2340948740034836</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05573518744640846</v>
+        <v>-0.05572379719676506</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3051989955065093</v>
+        <v>-0.3051969543323195</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1097312341929645</v>
+        <v>-0.1096837333923303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1734814964126597</v>
+        <v>0.173469812965979</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1570115804892578</v>
+        <v>-0.1570302824511975</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1550494139323269</v>
+        <v>-0.1550571636562038</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2369415134106761</v>
+        <v>-0.2369674996801849</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1015552657456527</v>
+        <v>-0.1015313952696612</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1124866067034826</v>
+        <v>0.1124595235492576</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01659728884541674</v>
+        <v>0.01658335414694034</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1919279369330885</v>
+        <v>-0.191896940440318</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.05267304410781847</v>
+        <v>-0.052700966008096</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03982221093887654</v>
+        <v>0.03979869880352869</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1229926994810185</v>
+        <v>-0.1230005545376402</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02109570603491869</v>
+        <v>-0.02111232513816038</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1694811327131412</v>
+        <v>-0.1695097466310259</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2321315893074772</v>
+        <v>-0.2321303204935241</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.02313709191950039</v>
+        <v>-0.02313206125994956</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1952861849636394</v>
+        <v>-0.1952972150142807</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1570115804892578</v>
+        <v>-0.1570302824511975</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05261010755270113</v>
+        <v>0.05258808827279601</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1596401763688102</v>
+        <v>-0.1596550024378361</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1584342378766951</v>
+        <v>-0.158436747149761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.05462073718364463</v>
+        <v>-0.05465406025743533</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1185884929584484</v>
+        <v>0.1185697315676807</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.03521084452182585</v>
+        <v>-0.03521630600510597</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.05065353979587778</v>
+        <v>-0.0507134191182562</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08191325254965322</v>
+        <v>-0.08192416750336802</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.09364851176332502</v>
+        <v>-0.09366840335879653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1109258512467372</v>
+        <v>0.1109122680466117</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04277182292514164</v>
+        <v>-0.04278871258701188</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1655304823325387</v>
+        <v>-0.165532756468342</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1139587847293489</v>
+        <v>-0.1139394003759898</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04410558767273976</v>
+        <v>0.04410149889114259</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1550494139323269</v>
+        <v>-0.1550571636562038</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05261010755270113</v>
+        <v>0.05258808827279601</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1653000277831697</v>
+        <v>-0.1653266940261403</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1003636677635154</v>
+        <v>-0.1003496838603702</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2697197635757724</v>
+        <v>-0.2697720832656767</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2206131884662203</v>
+        <v>-0.2206371140703807</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01844472575356932</v>
+        <v>-0.01844374248610745</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04057443313802659</v>
+        <v>0.04054986895626235</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06768521643960035</v>
+        <v>-0.06767357511572947</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.06971627868793651</v>
+        <v>-0.06975081974803478</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02217795087098894</v>
+        <v>-0.02224546256905153</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03566434765378478</v>
+        <v>-0.03568942120521505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2209893209640608</v>
+        <v>0.2209778772288461</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.08547020016791816</v>
+        <v>-0.08544757584878435</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.002172860838622796</v>
+        <v>-0.002162432814843489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2369415134106761</v>
+        <v>-0.2369674996801849</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1596401763688102</v>
+        <v>-0.1596550024378361</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1653000277831697</v>
+        <v>-0.1653266940261403</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.00456759139080658</v>
+        <v>-0.004567577773555279</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.01636665183167948</v>
+        <v>-0.01642797420305434</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1083412959202304</v>
+        <v>-0.1083781108491528</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.08338738388968313</v>
+        <v>-0.08338324555920362</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07609996114127029</v>
+        <v>0.07609389331246709</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01919493272810242</v>
+        <v>0.01921096076280788</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1607723438690446</v>
+        <v>-0.1607676022211366</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01107998381285726</v>
+        <v>0.01107258347005919</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1397350494004991</v>
+        <v>-0.1397131785997564</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.09863082897096562</v>
+        <v>-0.09861107588431545</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06756494252738353</v>
+        <v>-0.06751475648162174</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09602905280759723</v>
+        <v>0.09603059014993211</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1015552657456527</v>
+        <v>-0.1015313952696612</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1584342378766951</v>
+        <v>-0.158436747149761</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1003636677635154</v>
+        <v>-0.1003496838603702</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.00456759139080658</v>
+        <v>-0.004567577773555279</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04469953771778331</v>
+        <v>-0.04470734205513757</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07487827068185442</v>
+        <v>0.07488344303007086</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.249275637493331</v>
+        <v>-0.2492330792258951</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1054814559487131</v>
+        <v>0.1054837494481909</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.009079565232523209</v>
+        <v>-0.009060707402556005</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.05529987669693862</v>
+        <v>-0.05535635682487677</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1706482024768659</v>
+        <v>-0.1707802198543243</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01211746941085413</v>
+        <v>0.01209289242684258</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02044944977386697</v>
+        <v>0.02042202968406572</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1521685471683165</v>
+        <v>-0.1521419069686895</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02632978628227742</v>
+        <v>-0.02634511499826643</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1124866067034826</v>
+        <v>0.1124595235492576</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.05462073718364463</v>
+        <v>-0.05465406025743533</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2697197635757724</v>
+        <v>-0.2697720832656767</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01636665183167948</v>
+        <v>-0.01642797420305434</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04469953771778331</v>
+        <v>-0.04470734205513757</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1033252162677227</v>
+        <v>0.1032785423030003</v>
       </c>
       <c r="P14" t="n">
-        <v>0.007164462626643145</v>
+        <v>0.007171379270090678</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.06428248416788566</v>
+        <v>0.06424130348455404</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1850370713545271</v>
+        <v>-0.1850380856965045</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001859152292805254</v>
+        <v>0.0001575688712157499</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1581607847017404</v>
+        <v>-0.158230431397335</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06957417140905643</v>
+        <v>0.06956125056231488</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04714341253182439</v>
+        <v>0.04713154118594869</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3494179731108781</v>
+        <v>-0.3493936335799296</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01338062164499971</v>
+        <v>-0.01339056438744992</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01659728884541674</v>
+        <v>0.01658335414694034</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1185884929584484</v>
+        <v>0.1185697315676807</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2206131884662203</v>
+        <v>-0.2206371140703807</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1083412959202304</v>
+        <v>-0.1083781108491528</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07487827068185442</v>
+        <v>0.07488344303007086</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1033252162677227</v>
+        <v>0.1032785423030003</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.02345300960633107</v>
+        <v>-0.02344989652193676</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06149622363408948</v>
+        <v>0.06146901302650035</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01211476857481954</v>
+        <v>-0.01210583301429007</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.03787463396277559</v>
+        <v>-0.03786636611734018</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2380476139683421</v>
+        <v>-0.2380113065651576</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1309002494549707</v>
+        <v>0.130899514453913</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2065042327310006</v>
+        <v>0.2065254987050177</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.01584838218885036</v>
+        <v>-0.01580446138126519</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3928312768685449</v>
+        <v>-0.3927946649926491</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1919279369330885</v>
+        <v>-0.191896940440318</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03521084452182585</v>
+        <v>-0.03521630600510597</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01844472575356932</v>
+        <v>-0.01844374248610745</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.08338738388968313</v>
+        <v>-0.08338324555920362</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.249275637493331</v>
+        <v>-0.2492330792258951</v>
       </c>
       <c r="N16" t="n">
-        <v>0.007164462626643145</v>
+        <v>0.007171379270090678</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.02345300960633107</v>
+        <v>-0.02344989652193676</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1694297480538222</v>
+        <v>-0.1694390513134775</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2318477249768466</v>
+        <v>-0.2318910839135059</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.03085668974852612</v>
+        <v>-0.03086107200159248</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1241041926183611</v>
+        <v>-0.1241424911481934</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.278697039808761</v>
+        <v>-0.2787404821215865</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08803049607792637</v>
+        <v>-0.08802255843130408</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1450644622661627</v>
+        <v>-0.1450563541036886</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06485449697988024</v>
+        <v>-0.06487133062601888</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05267304410781847</v>
+        <v>-0.052700966008096</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.05065353979587778</v>
+        <v>-0.0507134191182562</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04057443313802659</v>
+        <v>0.04054986895626235</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07609996114127029</v>
+        <v>0.07609389331246709</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1054814559487131</v>
+        <v>0.1054837494481909</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06428248416788566</v>
+        <v>0.06424130348455404</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06149622363408948</v>
+        <v>0.06146901302650035</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1694297480538222</v>
+        <v>-0.1694390513134775</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
